--- a/Excel_files/single_neuron.xlsx
+++ b/Excel_files/single_neuron.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\udickman\SNNAPinNEURON\ErrorAnalysis\Excel_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\udickman\pySNNAP\Excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC07C6C5-3FA6-43CA-AFE8-B6B332DB4DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01489C3-F539-4E16-B4B8-2688729C29D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="716" activeTab="1" xr2:uid="{F0735362-4961-42D4-9F52-DCA2C5A03203}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="716" activeTab="1" xr2:uid="{F0735362-4961-42D4-9F52-DCA2C5A03203}"/>
   </bookViews>
   <sheets>
     <sheet name="Neu" sheetId="3" r:id="rId1"/>
@@ -15089,13 +15089,13 @@
         <v>153</v>
       </c>
       <c r="C28" s="17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D28" s="17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E28" s="17">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G28" s="17"/>
       <c r="H28" s="17"/>
